--- a/members.xlsx
+++ b/members.xlsx
@@ -1,12 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr/>
+  <bookViews>
+    <workbookView xWindow="132" yWindow="552" windowWidth="22716" windowHeight="9468"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -517,9 +520,6 @@
     <t>prerna.25bce11041@vitbhopal.ac.in</t>
   </si>
   <si>
-    <t>PRAGALBHA PADHE</t>
-  </si>
-  <si>
     <t>DESIGNING</t>
   </si>
   <si>
@@ -584,103 +584,121 @@
   </si>
   <si>
     <t>sunku.25bai10164@vitbhopal.ac.in</t>
+  </si>
+  <si>
+    <t>PRAGALBHA PADHY</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="18">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Roboto"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color rgb="FF434343"/>
       <name val="Roboto"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color rgb="FFFFCFC9"/>
       <name val="Roboto"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF434343"/>
       <name val="Roboto"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color rgb="FF0D593A"/>
       <name val="Roboto"/>
     </font>
     <font>
       <b/>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF1F1F1F"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
       <u/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FF434343"/>
       <name val="Roboto"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color rgb="FF24260A"/>
       <name val="Roboto"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color rgb="FF555917"/>
       <name val="Roboto"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color rgb="FF146C2E"/>
       <name val="Roboto"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color rgb="FF473821"/>
       <name val="Roboto"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color rgb="FF3C4043"/>
       <name val="Roboto"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color rgb="FFE8EAED"/>
       <name val="Roboto"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -691,7 +709,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -713,7 +731,13 @@
     </fill>
   </fills>
   <borders count="24">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="medium">
         <color rgb="FF000000"/>
@@ -727,6 +751,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -741,6 +766,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -755,6 +781,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -769,6 +796,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -783,6 +811,7 @@
       <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -797,6 +826,7 @@
       <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -811,6 +841,7 @@
       <bottom style="thin">
         <color rgb="FFFFFFFF"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -825,11 +856,16 @@
       <bottom style="thin">
         <color rgb="FFFFFFFF"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
         <color rgb="FF000000"/>
       </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -844,6 +880,7 @@
       <bottom style="thick">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -858,6 +895,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -866,9 +904,11 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -883,6 +923,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -894,6 +935,8 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -905,6 +948,8 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
@@ -919,6 +964,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -933,19 +979,23 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
         <color rgb="FF000000"/>
       </left>
+      <right/>
       <top style="medium">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -955,19 +1005,23 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
         <color rgb="FF000000"/>
       </left>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -977,19 +1031,23 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="medium">
         <color rgb="FF000000"/>
       </left>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -999,307 +1057,265 @@
       <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="85">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="2" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="2" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="2" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="3" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="4" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="4" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="4" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="3" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="4" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="4" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="4" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="4" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="5" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="6" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="6" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="6" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="2" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="2" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="2" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="4" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="4" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="4" fillId="3" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="3" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="4" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="4" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="4" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="3" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="2" fillId="2" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="2" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="4" fillId="3" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="4" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="4" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="7" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="8" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="8" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="2" fillId="3" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="9" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="4" fillId="2" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="4" fillId="3" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="5" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="10" fillId="3" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="6" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="6" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="11" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="12" fillId="2" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="13" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="13" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="14" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="15" fillId="3" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="15" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="5" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="10" fillId="3" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="16" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="12" fillId="3" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="17" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="17" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="4" fillId="2" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="2" fillId="2" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="4" fillId="3" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="4" fillId="2" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="2" fillId="2" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="4" fillId="3" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="4" fillId="2" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="4" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="15" fillId="3" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="15" fillId="3" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="18" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="2" fillId="2" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="19" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="20" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="4" fillId="2" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="21" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="20" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="21" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="22" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="6" fillId="2" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="23" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="12" fillId="0" fontId="17" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF535FC1"/>
-          <bgColor rgb="FF535FC1"/>
-        </patternFill>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF6F8F9"/>
-          <bgColor rgb="FFF6F8F9"/>
-        </patternFill>
-      </fill>
-      <border/>
-    </dxf>
+  <dxfs count="4">
     <dxf>
       <border>
         <left style="thin">
@@ -1316,20 +1332,45 @@
         </bottom>
       </border>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF6F8F9"/>
+          <bgColor rgb="FFF6F8F9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF535FC1"/>
+          <bgColor rgb="FF535FC1"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="1">
-    <tableStyle count="4" pivot="0" name="Sheet1-style">
-      <tableStyleElement dxfId="1" type="headerRow"/>
-      <tableStyleElement dxfId="2" type="firstRowStripe"/>
-      <tableStyleElement dxfId="3" type="secondRowStripe"/>
-      <tableStyleElement dxfId="4" size="0" type="wholeTable"/>
+    <tableStyle name="Sheet1-style" pivot="0" count="4">
+      <tableStyleElement type="wholeTable" size="0" dxfId="0"/>
+      <tableStyleElement type="headerRow" dxfId="3"/>
+      <tableStyleElement type="firstRowStripe" dxfId="2"/>
+      <tableStyleElement type="secondRowStripe" dxfId="1"/>
     </tableStyle>
   </tableStyles>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1337,20 +1378,20 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:E83" displayName="TENURE_2026" name="TENURE_2026" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TENURE_2026" displayName="TENURE_2026" ref="A1:E83">
   <tableColumns count="5">
-    <tableColumn name="Name" id="1"/>
-    <tableColumn name="Team" id="2"/>
-    <tableColumn name="Position" id="3"/>
-    <tableColumn name="Contact" id="4"/>
-    <tableColumn name="Email ID" id="5"/>
+    <tableColumn id="1" name="Name"/>
+    <tableColumn id="2" name="Team"/>
+    <tableColumn id="3" name="Position"/>
+    <tableColumn id="4" name="Contact"/>
+    <tableColumn id="5" name="Email ID"/>
   </tableColumns>
-  <tableStyleInfo name="Sheet1-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="Sheet1-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -1540,24 +1581,27 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:I84"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="33.25"/>
-    <col customWidth="1" min="2" max="2" width="29.38"/>
-    <col customWidth="1" min="3" max="3" width="23.25"/>
-    <col customWidth="1" min="4" max="4" width="14.5"/>
-    <col customWidth="1" min="5" max="5" width="36.75"/>
+    <col min="1" max="1" width="33.21875" customWidth="1"/>
+    <col min="2" max="2" width="29.33203125" customWidth="1"/>
+    <col min="3" max="3" width="23.21875" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" customWidth="1"/>
+    <col min="5" max="5" width="36.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" customHeight="1">
+    <row r="1" spans="1:5" ht="22.5" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1574,7 +1618,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" ht="22.5" customHeight="1">
+    <row r="2" spans="1:5" ht="22.5" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -1585,13 +1629,13 @@
         <v>7</v>
       </c>
       <c r="D2" s="5">
-        <v>7.023987458E9</v>
+        <v>7023987458</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" ht="22.5" customHeight="1">
+    <row r="3" spans="1:5" ht="22.5" customHeight="1">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
@@ -1602,13 +1646,13 @@
         <v>10</v>
       </c>
       <c r="D3" s="9">
-        <v>9.131707895E9</v>
+        <v>9131707895</v>
       </c>
       <c r="E3" s="9" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" ht="22.5" customHeight="1">
+    <row r="4" spans="1:5" ht="22.5" customHeight="1">
       <c r="A4" s="10" t="s">
         <v>12</v>
       </c>
@@ -1619,13 +1663,13 @@
         <v>13</v>
       </c>
       <c r="D4" s="13">
-        <v>9.327453822E9</v>
+        <v>9327453822</v>
       </c>
       <c r="E4" s="13" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" ht="22.5" customHeight="1">
+    <row r="5" spans="1:5" ht="22.5" customHeight="1">
       <c r="A5" s="6" t="s">
         <v>15</v>
       </c>
@@ -1636,13 +1680,13 @@
         <v>17</v>
       </c>
       <c r="D5" s="9">
-        <v>9.426151944E9</v>
+        <v>9426151944</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="6" ht="22.5" customHeight="1">
+    <row r="6" spans="1:5" ht="22.5" customHeight="1">
       <c r="A6" s="15" t="s">
         <v>19</v>
       </c>
@@ -1653,13 +1697,13 @@
         <v>20</v>
       </c>
       <c r="D6" s="18">
-        <v>9.974408009E9</v>
+        <v>9974408009</v>
       </c>
       <c r="E6" s="18" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="7" ht="22.5" customHeight="1">
+    <row r="7" spans="1:5" ht="22.5" customHeight="1">
       <c r="A7" s="19" t="s">
         <v>22</v>
       </c>
@@ -1670,13 +1714,13 @@
         <v>24</v>
       </c>
       <c r="D7" s="22">
-        <v>9.826633255E9</v>
+        <v>9826633255</v>
       </c>
       <c r="E7" s="23" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="8" ht="22.5" customHeight="1">
+    <row r="8" spans="1:5" ht="22.5" customHeight="1">
       <c r="A8" s="10" t="s">
         <v>26</v>
       </c>
@@ -1687,13 +1731,13 @@
         <v>27</v>
       </c>
       <c r="D8" s="13">
-        <v>8.210993912E9</v>
+        <v>8210993912</v>
       </c>
       <c r="E8" s="13" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="9" ht="22.5" customHeight="1">
+    <row r="9" spans="1:5" ht="22.5" customHeight="1">
       <c r="A9" s="10" t="s">
         <v>29</v>
       </c>
@@ -1704,13 +1748,13 @@
         <v>30</v>
       </c>
       <c r="D9" s="9">
-        <v>9.981772693E9</v>
+        <v>9981772693</v>
       </c>
       <c r="E9" s="26" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="10" ht="22.5" customHeight="1">
+    <row r="10" spans="1:5" ht="22.5" customHeight="1">
       <c r="A10" s="10" t="s">
         <v>32</v>
       </c>
@@ -1721,13 +1765,13 @@
         <v>30</v>
       </c>
       <c r="D10" s="13">
-        <v>8.528855254E9</v>
+        <v>8528855254</v>
       </c>
       <c r="E10" s="13" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="11" ht="22.5" customHeight="1">
+    <row r="11" spans="1:5" ht="22.5" customHeight="1">
       <c r="A11" s="10" t="s">
         <v>34</v>
       </c>
@@ -1738,13 +1782,13 @@
         <v>30</v>
       </c>
       <c r="D11" s="9">
-        <v>7.905227674E9</v>
+        <v>7905227674</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="12" ht="22.5" customHeight="1">
+    <row r="12" spans="1:5" ht="22.5" customHeight="1">
       <c r="A12" s="10" t="s">
         <v>36</v>
       </c>
@@ -1755,13 +1799,13 @@
         <v>30</v>
       </c>
       <c r="D12" s="13">
-        <v>7.970096783E9</v>
+        <v>7970096783</v>
       </c>
       <c r="E12" s="13" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="13" ht="22.5" customHeight="1">
+    <row r="13" spans="1:5" ht="22.5" customHeight="1">
       <c r="A13" s="27" t="s">
         <v>38</v>
       </c>
@@ -1772,13 +1816,13 @@
         <v>30</v>
       </c>
       <c r="D13" s="9">
-        <v>9.636743927E9</v>
+        <v>9636743927</v>
       </c>
       <c r="E13" s="28" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="14" ht="22.5" customHeight="1">
+    <row r="14" spans="1:5" ht="22.5" customHeight="1">
       <c r="A14" s="27" t="s">
         <v>40</v>
       </c>
@@ -1789,13 +1833,13 @@
         <v>30</v>
       </c>
       <c r="D14" s="9">
-        <v>9.108789822E9</v>
+        <v>9108789822</v>
       </c>
       <c r="E14" s="28" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="15" ht="22.5" customHeight="1">
+    <row r="15" spans="1:5" ht="22.5" customHeight="1">
       <c r="A15" s="27" t="s">
         <v>42</v>
       </c>
@@ -1806,13 +1850,13 @@
         <v>30</v>
       </c>
       <c r="D15" s="9">
-        <v>8.88760947E9</v>
+        <v>8887609470</v>
       </c>
       <c r="E15" s="28" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="16" ht="22.5" customHeight="1">
+    <row r="16" spans="1:5" ht="22.5" customHeight="1">
       <c r="A16" s="27" t="s">
         <v>44</v>
       </c>
@@ -1823,13 +1867,13 @@
         <v>30</v>
       </c>
       <c r="D16" s="9">
-        <v>9.238042934E9</v>
+        <v>9238042934</v>
       </c>
       <c r="E16" s="28" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="17" ht="22.5" customHeight="1">
+    <row r="17" spans="1:9" ht="22.5" customHeight="1">
       <c r="A17" s="27" t="s">
         <v>46</v>
       </c>
@@ -1840,7 +1884,7 @@
         <v>30</v>
       </c>
       <c r="D17" s="9">
-        <v>9.749445155E9</v>
+        <v>9749445155</v>
       </c>
       <c r="E17" s="28" t="s">
         <v>47</v>
@@ -1849,7 +1893,7 @@
       <c r="H17" s="29"/>
       <c r="I17" s="30"/>
     </row>
-    <row r="18" ht="22.5" customHeight="1">
+    <row r="18" spans="1:9" ht="22.5" customHeight="1">
       <c r="A18" s="27" t="s">
         <v>48</v>
       </c>
@@ -1860,7 +1904,7 @@
         <v>30</v>
       </c>
       <c r="D18" s="9">
-        <v>8.240568013E9</v>
+        <v>8240568013</v>
       </c>
       <c r="E18" s="28" t="s">
         <v>49</v>
@@ -1869,7 +1913,7 @@
       <c r="H18" s="31"/>
       <c r="I18" s="32"/>
     </row>
-    <row r="19" ht="22.5" customHeight="1">
+    <row r="19" spans="1:9" ht="22.5" customHeight="1">
       <c r="A19" s="27" t="s">
         <v>50</v>
       </c>
@@ -1880,7 +1924,7 @@
         <v>30</v>
       </c>
       <c r="D19" s="9">
-        <v>9.305395169E9</v>
+        <v>9305395169</v>
       </c>
       <c r="E19" s="28" t="s">
         <v>51</v>
@@ -1889,7 +1933,7 @@
       <c r="H19" s="29"/>
       <c r="I19" s="30"/>
     </row>
-    <row r="20" ht="22.5" customHeight="1">
+    <row r="20" spans="1:9" ht="22.5" customHeight="1">
       <c r="A20" s="27" t="s">
         <v>52</v>
       </c>
@@ -1900,7 +1944,7 @@
         <v>30</v>
       </c>
       <c r="D20" s="9">
-        <v>8.591179325E9</v>
+        <v>8591179325</v>
       </c>
       <c r="E20" s="28" t="s">
         <v>53</v>
@@ -1909,7 +1953,7 @@
       <c r="H20" s="31"/>
       <c r="I20" s="32"/>
     </row>
-    <row r="21" ht="22.5" customHeight="1">
+    <row r="21" spans="1:9" ht="22.5" customHeight="1">
       <c r="A21" s="27" t="s">
         <v>54</v>
       </c>
@@ -1920,7 +1964,7 @@
         <v>30</v>
       </c>
       <c r="D21" s="9">
-        <v>8.075306043E9</v>
+        <v>8075306043</v>
       </c>
       <c r="E21" s="28" t="s">
         <v>55</v>
@@ -1929,7 +1973,7 @@
       <c r="H21" s="29"/>
       <c r="I21" s="30"/>
     </row>
-    <row r="22" ht="22.5" customHeight="1">
+    <row r="22" spans="1:9" ht="22.5" customHeight="1">
       <c r="A22" s="27" t="s">
         <v>56</v>
       </c>
@@ -1940,7 +1984,7 @@
         <v>30</v>
       </c>
       <c r="D22" s="9">
-        <v>9.993345352E9</v>
+        <v>9993345352</v>
       </c>
       <c r="E22" s="28" t="s">
         <v>57</v>
@@ -1949,7 +1993,7 @@
       <c r="H22" s="29"/>
       <c r="I22" s="30"/>
     </row>
-    <row r="23" ht="22.5" customHeight="1">
+    <row r="23" spans="1:9" ht="22.5" customHeight="1">
       <c r="A23" s="27" t="s">
         <v>58</v>
       </c>
@@ -1960,7 +2004,7 @@
         <v>30</v>
       </c>
       <c r="D23" s="9">
-        <v>8.962303206E9</v>
+        <v>8962303206</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>59</v>
@@ -1969,7 +2013,7 @@
       <c r="H23" s="31"/>
       <c r="I23" s="32"/>
     </row>
-    <row r="24" ht="22.5" customHeight="1">
+    <row r="24" spans="1:9" ht="22.5" customHeight="1">
       <c r="A24" s="33" t="s">
         <v>60</v>
       </c>
@@ -1980,7 +2024,7 @@
         <v>30</v>
       </c>
       <c r="D24" s="13">
-        <v>8.950700275E9</v>
+        <v>8950700275</v>
       </c>
       <c r="E24" s="13" t="s">
         <v>61</v>
@@ -1989,7 +2033,7 @@
       <c r="H24" s="29"/>
       <c r="I24" s="30"/>
     </row>
-    <row r="25" ht="22.5" customHeight="1">
+    <row r="25" spans="1:9" ht="22.5" customHeight="1">
       <c r="A25" s="27" t="s">
         <v>62</v>
       </c>
@@ -2000,7 +2044,7 @@
         <v>30</v>
       </c>
       <c r="D25" s="9">
-        <v>7.033035694E9</v>
+        <v>7033035694</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>63</v>
@@ -2009,7 +2053,7 @@
       <c r="H25" s="31"/>
       <c r="I25" s="32"/>
     </row>
-    <row r="26" ht="22.5" customHeight="1">
+    <row r="26" spans="1:9" ht="22.5" customHeight="1">
       <c r="A26" s="33" t="s">
         <v>64</v>
       </c>
@@ -2020,7 +2064,7 @@
         <v>30</v>
       </c>
       <c r="D26" s="13">
-        <v>6.207425921E9</v>
+        <v>6207425921</v>
       </c>
       <c r="E26" s="13" t="s">
         <v>65</v>
@@ -2029,7 +2073,7 @@
       <c r="H26" s="29"/>
       <c r="I26" s="30"/>
     </row>
-    <row r="27" ht="22.5" customHeight="1">
+    <row r="27" spans="1:9" ht="22.5" customHeight="1">
       <c r="A27" s="2" t="s">
         <v>66</v>
       </c>
@@ -2040,13 +2084,13 @@
         <v>24</v>
       </c>
       <c r="D27" s="5">
-        <v>6.202706348E9</v>
+        <v>6202706348</v>
       </c>
       <c r="E27" s="5" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="28" ht="22.5" customHeight="1">
+    <row r="28" spans="1:9" ht="22.5" customHeight="1">
       <c r="A28" s="6" t="s">
         <v>69</v>
       </c>
@@ -2057,13 +2101,13 @@
         <v>27</v>
       </c>
       <c r="D28" s="9">
-        <v>7.35516296E9</v>
+        <v>7355162960</v>
       </c>
       <c r="E28" s="9" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="29" ht="22.5" customHeight="1">
+    <row r="29" spans="1:9" ht="22.5" customHeight="1">
       <c r="A29" s="33" t="s">
         <v>71</v>
       </c>
@@ -2074,13 +2118,13 @@
         <v>30</v>
       </c>
       <c r="D29" s="13">
-        <v>8.789579369E9</v>
+        <v>8789579369</v>
       </c>
       <c r="E29" s="13" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="30" ht="22.5" customHeight="1">
+    <row r="30" spans="1:9" ht="22.5" customHeight="1">
       <c r="A30" s="27" t="s">
         <v>73</v>
       </c>
@@ -2091,13 +2135,13 @@
         <v>30</v>
       </c>
       <c r="D30" s="9">
-        <v>7.819095799E9</v>
+        <v>7819095799</v>
       </c>
       <c r="E30" s="9" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="31" ht="22.5" customHeight="1">
+    <row r="31" spans="1:9" ht="22.5" customHeight="1">
       <c r="A31" s="33" t="s">
         <v>75</v>
       </c>
@@ -2108,13 +2152,13 @@
         <v>30</v>
       </c>
       <c r="D31" s="13">
-        <v>8.329543495E9</v>
+        <v>8329543495</v>
       </c>
       <c r="E31" s="13" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="32" ht="22.5" customHeight="1">
+    <row r="32" spans="1:9" ht="22.5" customHeight="1">
       <c r="A32" s="27" t="s">
         <v>77</v>
       </c>
@@ -2125,13 +2169,13 @@
         <v>30</v>
       </c>
       <c r="D32" s="9">
-        <v>7.054094364E9</v>
+        <v>7054094364</v>
       </c>
       <c r="E32" s="9" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="33" ht="22.5" customHeight="1">
+    <row r="33" spans="1:5" ht="22.5" customHeight="1">
       <c r="A33" s="39" t="s">
         <v>79</v>
       </c>
@@ -2142,13 +2186,13 @@
         <v>30</v>
       </c>
       <c r="D33" s="41">
-        <v>8.103028616E9</v>
+        <v>8103028616</v>
       </c>
       <c r="E33" s="41" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="34" ht="22.5" customHeight="1">
+    <row r="34" spans="1:5" ht="22.5" customHeight="1">
       <c r="A34" s="19" t="s">
         <v>81</v>
       </c>
@@ -2159,13 +2203,13 @@
         <v>83</v>
       </c>
       <c r="D34" s="23">
-        <v>9.075002766E9</v>
+        <v>9075002766</v>
       </c>
       <c r="E34" s="23" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="35" ht="22.5" customHeight="1">
+    <row r="35" spans="1:5" ht="22.5" customHeight="1">
       <c r="A35" s="43" t="s">
         <v>85</v>
       </c>
@@ -2176,13 +2220,13 @@
         <v>86</v>
       </c>
       <c r="D35" s="13">
-        <v>9.321032168E9</v>
+        <v>9321032168</v>
       </c>
       <c r="E35" s="13" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="36" ht="22.5" customHeight="1">
+    <row r="36" spans="1:5" ht="22.5" customHeight="1">
       <c r="A36" s="6" t="s">
         <v>88</v>
       </c>
@@ -2193,13 +2237,13 @@
         <v>89</v>
       </c>
       <c r="D36" s="22">
-        <v>8.719074752E9</v>
+        <v>8719074752</v>
       </c>
       <c r="E36" s="9" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="37" ht="22.5" customHeight="1">
+    <row r="37" spans="1:5" ht="22.5" customHeight="1">
       <c r="A37" s="6" t="s">
         <v>91</v>
       </c>
@@ -2210,13 +2254,13 @@
         <v>89</v>
       </c>
       <c r="D37" s="9">
-        <v>7.985816996E9</v>
+        <v>7985816996</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="38" ht="22.5" customHeight="1">
+    <row r="38" spans="1:5" ht="22.5" customHeight="1">
       <c r="A38" s="10" t="s">
         <v>93</v>
       </c>
@@ -2227,13 +2271,13 @@
         <v>89</v>
       </c>
       <c r="D38" s="13">
-        <v>8.708586504E9</v>
+        <v>8708586504</v>
       </c>
       <c r="E38" s="13" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="39" ht="22.5" customHeight="1">
+    <row r="39" spans="1:5" ht="22.5" customHeight="1">
       <c r="A39" s="6" t="s">
         <v>95</v>
       </c>
@@ -2244,13 +2288,13 @@
         <v>89</v>
       </c>
       <c r="D39" s="9">
-        <v>9.886700029E9</v>
+        <v>9886700029</v>
       </c>
       <c r="E39" s="13" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="40" ht="22.5" customHeight="1">
+    <row r="40" spans="1:5" ht="22.5" customHeight="1">
       <c r="A40" s="33" t="s">
         <v>97</v>
       </c>
@@ -2261,13 +2305,13 @@
         <v>89</v>
       </c>
       <c r="D40" s="13">
-        <v>8.077538321E9</v>
+        <v>8077538321</v>
       </c>
       <c r="E40" s="13" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="41" ht="22.5" customHeight="1">
+    <row r="41" spans="1:5" ht="22.5" customHeight="1">
       <c r="A41" s="33" t="s">
         <v>99</v>
       </c>
@@ -2278,13 +2322,13 @@
         <v>89</v>
       </c>
       <c r="D41" s="13">
-        <v>9.72995312E9</v>
+        <v>9729953120</v>
       </c>
       <c r="E41" s="13" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="42" ht="22.5" customHeight="1">
+    <row r="42" spans="1:5" ht="22.5" customHeight="1">
       <c r="A42" s="27" t="s">
         <v>101</v>
       </c>
@@ -2295,13 +2339,13 @@
         <v>89</v>
       </c>
       <c r="D42" s="9">
-        <v>6.376549494E9</v>
+        <v>6376549494</v>
       </c>
       <c r="E42" s="9" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="43" ht="22.5" customHeight="1">
+    <row r="43" spans="1:5" ht="22.5" customHeight="1">
       <c r="A43" s="33" t="s">
         <v>103</v>
       </c>
@@ -2312,13 +2356,13 @@
         <v>89</v>
       </c>
       <c r="D43" s="13">
-        <v>8.103499108E9</v>
+        <v>8103499108</v>
       </c>
       <c r="E43" s="13" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="44" ht="22.5" customHeight="1">
+    <row r="44" spans="1:5" ht="22.5" customHeight="1">
       <c r="A44" s="46" t="s">
         <v>105</v>
       </c>
@@ -2329,13 +2373,13 @@
         <v>89</v>
       </c>
       <c r="D44" s="49">
-        <v>8.79897412E9</v>
+        <v>8798974120</v>
       </c>
       <c r="E44" s="49" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="45" ht="22.5" customHeight="1">
+    <row r="45" spans="1:5" ht="22.5" customHeight="1">
       <c r="A45" s="50" t="s">
         <v>107</v>
       </c>
@@ -2346,13 +2390,13 @@
         <v>108</v>
       </c>
       <c r="D45" s="53">
-        <v>7.389846047E9</v>
+        <v>7389846047</v>
       </c>
       <c r="E45" s="53" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="46" ht="22.5" customHeight="1">
+    <row r="46" spans="1:5" ht="22.5" customHeight="1">
       <c r="A46" s="6" t="s">
         <v>110</v>
       </c>
@@ -2363,13 +2407,13 @@
         <v>111</v>
       </c>
       <c r="D46" s="9">
-        <v>6.353086321E9</v>
+        <v>6353086321</v>
       </c>
       <c r="E46" s="9" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="47" ht="22.5" customHeight="1">
+    <row r="47" spans="1:5" ht="22.5" customHeight="1">
       <c r="A47" s="10" t="s">
         <v>113</v>
       </c>
@@ -2380,13 +2424,13 @@
         <v>111</v>
       </c>
       <c r="D47" s="13">
-        <v>8.78031922E9</v>
+        <v>8780319220</v>
       </c>
       <c r="E47" s="13" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="48" ht="22.5" customHeight="1">
+    <row r="48" spans="1:5" ht="22.5" customHeight="1">
       <c r="A48" s="6" t="s">
         <v>115</v>
       </c>
@@ -2397,13 +2441,13 @@
         <v>116</v>
       </c>
       <c r="D48" s="9">
-        <v>9.161780284E9</v>
+        <v>9161780284</v>
       </c>
       <c r="E48" s="9" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="49" ht="22.5" customHeight="1">
+    <row r="49" spans="1:5" ht="22.5" customHeight="1">
       <c r="A49" s="10" t="s">
         <v>118</v>
       </c>
@@ -2414,13 +2458,13 @@
         <v>116</v>
       </c>
       <c r="D49" s="13">
-        <v>8.172831412E9</v>
+        <v>8172831412</v>
       </c>
       <c r="E49" s="13" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="50" ht="22.5" customHeight="1">
+    <row r="50" spans="1:5" ht="22.5" customHeight="1">
       <c r="A50" s="6" t="s">
         <v>120</v>
       </c>
@@ -2431,13 +2475,13 @@
         <v>116</v>
       </c>
       <c r="D50" s="9">
-        <v>7.06341851E9</v>
+        <v>7063418510</v>
       </c>
       <c r="E50" s="9" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="51" ht="22.5" customHeight="1">
+    <row r="51" spans="1:5" ht="22.5" customHeight="1">
       <c r="A51" s="10" t="s">
         <v>122</v>
       </c>
@@ -2448,13 +2492,13 @@
         <v>116</v>
       </c>
       <c r="D51" s="13">
-        <v>6.29138846E9</v>
+        <v>6291388460</v>
       </c>
       <c r="E51" s="13" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="52" ht="22.5" customHeight="1">
+    <row r="52" spans="1:5" ht="22.5" customHeight="1">
       <c r="A52" s="10" t="s">
         <v>124</v>
       </c>
@@ -2465,13 +2509,13 @@
         <v>116</v>
       </c>
       <c r="D52" s="13">
-        <v>7.880118328E9</v>
+        <v>7880118328</v>
       </c>
       <c r="E52" s="13" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="53" ht="22.5" customHeight="1">
+    <row r="53" spans="1:5" ht="22.5" customHeight="1">
       <c r="A53" s="10" t="s">
         <v>126</v>
       </c>
@@ -2482,13 +2526,13 @@
         <v>116</v>
       </c>
       <c r="D53" s="9">
-        <v>9.243109266E9</v>
+        <v>9243109266</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="54" ht="22.5" customHeight="1">
+    <row r="54" spans="1:5" ht="22.5" customHeight="1">
       <c r="A54" s="54" t="s">
         <v>128</v>
       </c>
@@ -2499,13 +2543,13 @@
         <v>116</v>
       </c>
       <c r="D54" s="56">
-        <v>9.009986986E9</v>
+        <v>9009986986</v>
       </c>
       <c r="E54" s="56" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="55" ht="22.5" customHeight="1">
+    <row r="55" spans="1:5" ht="22.5" customHeight="1">
       <c r="A55" s="54" t="s">
         <v>130</v>
       </c>
@@ -2516,13 +2560,13 @@
         <v>116</v>
       </c>
       <c r="D55" s="56">
-        <v>9.351341433E9</v>
+        <v>9351341433</v>
       </c>
       <c r="E55" s="56" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="56" ht="22.5" customHeight="1">
+    <row r="56" spans="1:5" ht="22.5" customHeight="1">
       <c r="A56" s="54" t="s">
         <v>132</v>
       </c>
@@ -2533,13 +2577,13 @@
         <v>116</v>
       </c>
       <c r="D56" s="56">
-        <v>9.112261102E9</v>
+        <v>9112261102</v>
       </c>
       <c r="E56" s="56" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="57" ht="22.5" customHeight="1">
+    <row r="57" spans="1:5" ht="22.5" customHeight="1">
       <c r="A57" s="54" t="s">
         <v>134</v>
       </c>
@@ -2550,13 +2594,13 @@
         <v>116</v>
       </c>
       <c r="D57" s="56">
-        <v>9.251029572E9</v>
+        <v>9251029572</v>
       </c>
       <c r="E57" s="56" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="58" ht="22.5" customHeight="1">
+    <row r="58" spans="1:5" ht="22.5" customHeight="1">
       <c r="A58" s="57" t="s">
         <v>136</v>
       </c>
@@ -2567,13 +2611,13 @@
         <v>116</v>
       </c>
       <c r="D58" s="18">
-        <v>8.812838257E9</v>
+        <v>8812838257</v>
       </c>
       <c r="E58" s="18" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="59" ht="22.5" customHeight="1">
+    <row r="59" spans="1:5" ht="22.5" customHeight="1">
       <c r="A59" s="59" t="s">
         <v>138</v>
       </c>
@@ -2584,13 +2628,13 @@
         <v>24</v>
       </c>
       <c r="D59" s="62">
-        <v>6.267743046E9</v>
+        <v>6267743046</v>
       </c>
       <c r="E59" s="62" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="60" ht="22.5" customHeight="1">
+    <row r="60" spans="1:5" ht="22.5" customHeight="1">
       <c r="A60" s="10" t="s">
         <v>141</v>
       </c>
@@ -2601,13 +2645,13 @@
         <v>27</v>
       </c>
       <c r="D60" s="13">
-        <v>9.035764436E9</v>
+        <v>9035764436</v>
       </c>
       <c r="E60" s="13" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="61" ht="22.5" customHeight="1">
+    <row r="61" spans="1:5" ht="22.5" customHeight="1">
       <c r="A61" s="27" t="s">
         <v>143</v>
       </c>
@@ -2618,13 +2662,13 @@
         <v>30</v>
       </c>
       <c r="D61" s="9">
-        <v>8.35393164E9</v>
+        <v>8353931640</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="62" ht="22.5" customHeight="1">
+    <row r="62" spans="1:5" ht="22.5" customHeight="1">
       <c r="A62" s="33" t="s">
         <v>145</v>
       </c>
@@ -2635,13 +2679,13 @@
         <v>30</v>
       </c>
       <c r="D62" s="13">
-        <v>7.275013015E9</v>
+        <v>7275013015</v>
       </c>
       <c r="E62" s="13" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="63" ht="22.5" customHeight="1">
+    <row r="63" spans="1:5" ht="22.5" customHeight="1">
       <c r="A63" s="27" t="s">
         <v>147</v>
       </c>
@@ -2652,13 +2696,13 @@
         <v>30</v>
       </c>
       <c r="D63" s="9">
-        <v>6.359765797E9</v>
+        <v>6359765797</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="64" ht="22.5" customHeight="1">
+    <row r="64" spans="1:5" ht="22.5" customHeight="1">
       <c r="A64" s="33" t="s">
         <v>149</v>
       </c>
@@ -2669,13 +2713,13 @@
         <v>30</v>
       </c>
       <c r="D64" s="13">
-        <v>9.296117558E9</v>
+        <v>9296117558</v>
       </c>
       <c r="E64" s="13" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="65" ht="22.5" customHeight="1">
+    <row r="65" spans="1:5" ht="22.5" customHeight="1">
       <c r="A65" s="46" t="s">
         <v>151</v>
       </c>
@@ -2686,13 +2730,13 @@
         <v>30</v>
       </c>
       <c r="D65" s="49">
-        <v>6.35469797E9</v>
+        <v>6354697970</v>
       </c>
       <c r="E65" s="49" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="66" ht="22.5" customHeight="1">
+    <row r="66" spans="1:5" ht="22.5" customHeight="1">
       <c r="A66" s="2" t="s">
         <v>153</v>
       </c>
@@ -2703,13 +2747,13 @@
         <v>24</v>
       </c>
       <c r="D66" s="5">
-        <v>8.085087801E9</v>
+        <v>8085087801</v>
       </c>
       <c r="E66" s="5" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="67" ht="22.5" customHeight="1">
+    <row r="67" spans="1:5" ht="22.5" customHeight="1">
       <c r="A67" s="6" t="s">
         <v>156</v>
       </c>
@@ -2720,13 +2764,13 @@
         <v>27</v>
       </c>
       <c r="D67" s="9">
-        <v>8.00293807E9</v>
+        <v>8002938070</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="68" ht="22.5" customHeight="1">
+    <row r="68" spans="1:5" ht="22.5" customHeight="1">
       <c r="A68" s="10" t="s">
         <v>158</v>
       </c>
@@ -2737,13 +2781,13 @@
         <v>30</v>
       </c>
       <c r="D68" s="13">
-        <v>8.595220472E9</v>
+        <v>8595220472</v>
       </c>
       <c r="E68" s="13" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="69" ht="22.5" customHeight="1">
+    <row r="69" spans="1:5" ht="22.5" customHeight="1">
       <c r="A69" s="27" t="s">
         <v>160</v>
       </c>
@@ -2754,13 +2798,13 @@
         <v>30</v>
       </c>
       <c r="D69" s="9">
-        <v>7.749861498E9</v>
+        <v>7749861498</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="70" ht="22.5" customHeight="1">
+    <row r="70" spans="1:5" ht="22.5" customHeight="1">
       <c r="A70" s="33" t="s">
         <v>162</v>
       </c>
@@ -2771,13 +2815,13 @@
         <v>30</v>
       </c>
       <c r="D70" s="13">
-        <v>9.236165807E9</v>
+        <v>9236165807</v>
       </c>
       <c r="E70" s="13" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="71" ht="22.5" customHeight="1">
+    <row r="71" spans="1:5" ht="22.5" customHeight="1">
       <c r="A71" s="27" t="s">
         <v>164</v>
       </c>
@@ -2788,13 +2832,13 @@
         <v>30</v>
       </c>
       <c r="D71" s="9">
-        <v>9.41127467E9</v>
+        <v>9411274670</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="72" ht="22.5" customHeight="1">
+    <row r="72" spans="1:5" ht="22.5" customHeight="1">
       <c r="A72" s="33" t="s">
         <v>166</v>
       </c>
@@ -2805,214 +2849,214 @@
         <v>30</v>
       </c>
       <c r="D72" s="13">
-        <v>9.01716105E9</v>
+        <v>9017161050</v>
       </c>
       <c r="E72" s="13" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="73" ht="22.5" customHeight="1">
+    <row r="73" spans="1:5" ht="22.5" customHeight="1">
       <c r="A73" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="B73" s="67" t="s">
         <v>168</v>
-      </c>
-      <c r="B73" s="67" t="s">
-        <v>169</v>
       </c>
       <c r="C73" s="35" t="s">
         <v>24</v>
       </c>
       <c r="D73" s="5">
-        <v>9.938972584E9</v>
+        <v>9938972584</v>
       </c>
       <c r="E73" s="5" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" ht="22.5" customHeight="1">
+      <c r="A74" s="6" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="74" ht="22.5" customHeight="1">
-      <c r="A74" s="6" t="s">
-        <v>171</v>
-      </c>
       <c r="B74" s="68" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C74" s="8" t="s">
         <v>27</v>
       </c>
       <c r="D74" s="9">
-        <v>9.520913489E9</v>
+        <v>9520913489</v>
       </c>
       <c r="E74" s="9" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" ht="22.5" customHeight="1">
+      <c r="A75" s="10" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="75" ht="22.5" customHeight="1">
-      <c r="A75" s="10" t="s">
+      <c r="B75" s="69" t="s">
+        <v>168</v>
+      </c>
+      <c r="C75" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="D75" s="13">
+        <v>9125438555</v>
+      </c>
+      <c r="E75" s="13" t="s">
         <v>173</v>
       </c>
-      <c r="B75" s="69" t="s">
-        <v>169</v>
-      </c>
-      <c r="C75" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="D75" s="13">
-        <v>9.125438555E9</v>
-      </c>
-      <c r="E75" s="13" t="s">
+    </row>
+    <row r="76" spans="1:5" ht="22.5" customHeight="1">
+      <c r="A76" s="6" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="76" ht="22.5" customHeight="1">
-      <c r="A76" s="6" t="s">
+      <c r="B76" s="68" t="s">
+        <v>168</v>
+      </c>
+      <c r="C76" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D76" s="9">
+        <v>8296538921</v>
+      </c>
+      <c r="E76" s="70" t="s">
         <v>175</v>
       </c>
-      <c r="B76" s="68" t="s">
-        <v>169</v>
-      </c>
-      <c r="C76" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="D76" s="9">
-        <v>8.296538921E9</v>
-      </c>
-      <c r="E76" s="70" t="s">
+    </row>
+    <row r="77" spans="1:5" ht="22.5" customHeight="1">
+      <c r="A77" s="27" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="77" ht="22.5" customHeight="1">
-      <c r="A77" s="27" t="s">
+      <c r="B77" s="68" t="s">
+        <v>168</v>
+      </c>
+      <c r="C77" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D77" s="9">
+        <v>9339630842</v>
+      </c>
+      <c r="E77" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="B77" s="68" t="s">
-        <v>169</v>
-      </c>
-      <c r="C77" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="D77" s="9">
-        <v>9.339630842E9</v>
-      </c>
-      <c r="E77" s="9" t="s">
+    </row>
+    <row r="78" spans="1:5" ht="22.5" customHeight="1">
+      <c r="A78" s="27" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="78" ht="22.5" customHeight="1">
-      <c r="A78" s="27" t="s">
+      <c r="B78" s="71" t="s">
+        <v>168</v>
+      </c>
+      <c r="C78" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D78" s="9">
+        <v>9303713367</v>
+      </c>
+      <c r="E78" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="B78" s="71" t="s">
-        <v>169</v>
-      </c>
-      <c r="C78" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="D78" s="9">
-        <v>9.303713367E9</v>
-      </c>
-      <c r="E78" s="9" t="s">
+    </row>
+    <row r="79" spans="1:5" ht="22.5" customHeight="1">
+      <c r="A79" s="27" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="79" ht="22.5" customHeight="1">
-      <c r="A79" s="27" t="s">
+      <c r="B79" s="72" t="s">
+        <v>168</v>
+      </c>
+      <c r="C79" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D79" s="9">
+        <v>8484030955</v>
+      </c>
+      <c r="E79" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="B79" s="72" t="s">
-        <v>169</v>
-      </c>
-      <c r="C79" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="D79" s="9">
-        <v>8.484030955E9</v>
-      </c>
-      <c r="E79" s="9" t="s">
+    </row>
+    <row r="80" spans="1:5" ht="22.5" customHeight="1">
+      <c r="A80" s="73" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="80" ht="22.5" customHeight="1">
-      <c r="A80" s="73" t="s">
+      <c r="B80" s="74" t="s">
         <v>183</v>
-      </c>
-      <c r="B80" s="74" t="s">
-        <v>184</v>
       </c>
       <c r="C80" s="75" t="s">
         <v>24</v>
       </c>
       <c r="D80" s="5">
-        <v>9.931877713E9</v>
+        <v>9931877713</v>
       </c>
       <c r="E80" s="5" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" ht="22.5" customHeight="1">
+      <c r="A81" s="76" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="81" ht="22.5" customHeight="1">
-      <c r="A81" s="76" t="s">
+      <c r="B81" s="77" t="s">
+        <v>183</v>
+      </c>
+      <c r="C81" s="78" t="s">
+        <v>30</v>
+      </c>
+      <c r="D81" s="13">
+        <v>9695391306</v>
+      </c>
+      <c r="E81" s="13" t="s">
         <v>186</v>
       </c>
-      <c r="B81" s="77" t="s">
-        <v>184</v>
-      </c>
-      <c r="C81" s="78" t="s">
-        <v>30</v>
-      </c>
-      <c r="D81" s="13">
-        <v>9.695391306E9</v>
-      </c>
-      <c r="E81" s="13" t="s">
+    </row>
+    <row r="82" spans="1:5" ht="22.5" customHeight="1">
+      <c r="A82" s="79" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="82" ht="22.5" customHeight="1">
-      <c r="A82" s="79" t="s">
-        <v>188</v>
-      </c>
       <c r="B82" s="77" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C82" s="80" t="s">
         <v>30</v>
       </c>
       <c r="D82" s="9">
-        <v>9.993345352E9</v>
+        <v>9993345352</v>
       </c>
       <c r="E82" s="9" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="83" ht="22.5" customHeight="1">
+    <row r="83" spans="1:5" ht="22.5" customHeight="1">
       <c r="A83" s="81" t="s">
+        <v>188</v>
+      </c>
+      <c r="B83" s="82" t="s">
+        <v>183</v>
+      </c>
+      <c r="C83" s="83" t="s">
+        <v>30</v>
+      </c>
+      <c r="D83" s="18">
+        <v>9347183811</v>
+      </c>
+      <c r="E83" s="18" t="s">
         <v>189</v>
       </c>
-      <c r="B83" s="82" t="s">
-        <v>184</v>
-      </c>
-      <c r="C83" s="83" t="s">
-        <v>30</v>
-      </c>
-      <c r="D83" s="18">
-        <v>9.347183811E9</v>
-      </c>
-      <c r="E83" s="18" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="84">
+    </row>
+    <row r="84" spans="1:5" ht="13.2">
       <c r="B84" s="84"/>
     </row>
   </sheetData>
-  <dataValidations>
+  <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" sqref="B2:B83">
       <formula1>"PANEL MEMBER,OPERATIONS,ELETRONICS TEAM,PROGRAMMING TEAM,EVENT MANAGEMENT,PR AND OUTREACH,SOCIAL MEDIA,DESIGNING,CONTENT TEAM"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="E9"/>
+    <hyperlink ref="E9" r:id="rId1"/>
   </hyperlinks>
-  <drawing r:id="rId2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId4"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>